--- a/output/pdf_financials_xlsx/TONE.xlsx
+++ b/output/pdf_financials_xlsx/TONE.xlsx
@@ -2836,13 +2836,13 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>-0.00137</v>
+        <v>-0.037392</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.007215</v>
+        <v>-0.006473</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.118209</v>
+        <v>0.088209</v>
       </c>
     </row>
     <row r="119">
@@ -4400,7 +4400,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TONE.xlsx
+++ b/output/pdf_financials_xlsx/TONE.xlsx
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011179</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.012708</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.004006</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.316442</v>
       </c>
     </row>
     <row r="35">
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.011179</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.012708</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.004006</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.316442</v>
       </c>
     </row>
     <row r="37">
@@ -1399,16 +1399,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.011179</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.059008</v>
+        <v>0.0463</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.004006</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.316442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">

--- a/output/pdf_financials_xlsx/TONE.xlsx
+++ b/output/pdf_financials_xlsx/TONE.xlsx
@@ -555,10 +555,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.063428</v>
+        <v>0.08742800000000001</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.401102</v>
+        <v>0.404102</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.306879</v>
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.09148199999999999</v>
+        <v>0.115482</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.413152</v>
+        <v>0.416152</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.322299</v>
@@ -5420,7 +5420,11 @@
           <t>Director fees 8</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
